--- a/Ventas_Combustibles_Mexico.xlsx
+++ b/Ventas_Combustibles_Mexico.xlsx
@@ -9543,10 +9543,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>664.1</v>
+        <v>661.4</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>670.3</v>
+        <v>667.4</v>
       </c>
       <c r="G8" s="29" t="n">
         <v>608</v>
@@ -9555,16 +9555,16 @@
         <v>608</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>-6.2</v>
+        <v>-5.9</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>62.2</v>
+        <v>59.3</v>
       </c>
       <c r="K8" s="29" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="29" t="n">
-        <v>56.1</v>
+        <v>53.4</v>
       </c>
       <c r="M8" s="29" t="n"/>
       <c r="N8" s="29" t="n"/>
@@ -9588,10 +9588,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>538.7</v>
+        <v>541.9</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>539</v>
+        <v>532.7</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>507.7</v>
@@ -9600,22 +9600,22 @@
         <v>507.6</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>-0.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>31.3</v>
+        <v>24.9</v>
       </c>
       <c r="K9" s="18" t="n">
         <v>0.2</v>
       </c>
       <c r="L9" s="18" t="n">
-        <v>31.1</v>
+        <v>34.3</v>
       </c>
       <c r="M9" s="18" t="n">
-        <v>-18.9</v>
+        <v>-18.1</v>
       </c>
       <c r="N9" s="18" t="n">
-        <v>-19.6</v>
+        <v>-20.2</v>
       </c>
       <c r="O9" s="18" t="n">
         <v>-16.5</v>
@@ -9643,10 +9643,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>566</v>
+        <v>574.9</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>555.4</v>
+        <v>543.4</v>
       </c>
       <c r="G10" s="29" t="n">
         <v>559.7</v>
@@ -9655,22 +9655,22 @@
         <v>559.6</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>10.6</v>
+        <v>31.5</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>-4.3</v>
+        <v>-16.3</v>
       </c>
       <c r="K10" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="L10" s="29" t="n">
-        <v>6.4</v>
+        <v>15.3</v>
       </c>
       <c r="M10" s="29" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="N10" s="29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" s="29" t="n">
         <v>10.2</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>675.2</v>
+        <v>672.3</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>652.1</v>
+        <v>641.9</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>642.2</v>
@@ -9710,22 +9710,22 @@
         <v>642.1</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>23.1</v>
+        <v>30.4</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>9.800000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>33.1</v>
+        <v>30.2</v>
       </c>
       <c r="M11" s="18" t="n">
-        <v>19.3</v>
+        <v>16.9</v>
       </c>
       <c r="N11" s="18" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="O11" s="18" t="n">
         <v>14.7</v>
@@ -9753,10 +9753,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>666.1</v>
+        <v>668.5</v>
       </c>
       <c r="F12" s="29" t="n">
-        <v>634.3</v>
+        <v>622.8</v>
       </c>
       <c r="G12" s="29" t="n">
         <v>665.9</v>
@@ -9765,22 +9765,22 @@
         <v>665.8</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>31.8</v>
+        <v>45.7</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>-31.6</v>
+        <v>-43</v>
       </c>
       <c r="K12" s="29" t="n">
         <v>0.1</v>
       </c>
       <c r="L12" s="29" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="M12" s="29" t="n">
-        <v>-1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="N12" s="29" t="n">
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
       <c r="O12" s="29" t="n">
         <v>3.7</v>
@@ -9808,10 +9808,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>667.5</v>
+        <v>666.8</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>629</v>
+        <v>614.3</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>656.7</v>
@@ -9820,22 +9820,22 @@
         <v>656.6</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>38.5</v>
+        <v>52.5</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>-27.7</v>
+        <v>-42.4</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>-0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="O13" s="18" t="n">
         <v>-1.4</v>
@@ -9863,10 +9863,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>645.8</v>
+        <v>642.7</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="G14" s="29" t="n">
         <v>621.1</v>
@@ -9875,22 +9875,22 @@
         <v>621</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>37.8</v>
+        <v>56.7</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>-13.2</v>
+        <v>-35.1</v>
       </c>
       <c r="K14" s="29" t="n">
         <v>0.1</v>
       </c>
       <c r="L14" s="29" t="n">
-        <v>24.7</v>
+        <v>21.7</v>
       </c>
       <c r="M14" s="29" t="n">
-        <v>-3.3</v>
+        <v>-3.6</v>
       </c>
       <c r="N14" s="29" t="n">
-        <v>-3.3</v>
+        <v>-4.6</v>
       </c>
       <c r="O14" s="29" t="n">
         <v>-5.4</v>
@@ -9918,10 +9918,10 @@
         <v>2</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>691.6</v>
+        <v>680.7</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>681.7</v>
+        <v>660.2</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>652</v>
@@ -9930,22 +9930,22 @@
         <v>651.9</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>9.9</v>
+        <v>20.5</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>29.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>39.8</v>
+        <v>28.8</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="O15" s="18" t="n">
         <v>5</v>
@@ -10067,10 +10067,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>123.1</v>
+        <v>125.7</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>123.9</v>
+        <v>126.8</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>115.4</v>
@@ -10079,16 +10079,16 @@
         <v>115.4</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>7.7</v>
+        <v>10.3</v>
       </c>
       <c r="M19" s="18" t="n"/>
       <c r="N19" s="18" t="n"/>
@@ -10112,10 +10112,10 @@
         <v>0</v>
       </c>
       <c r="E20" s="29" t="n">
-        <v>132.9</v>
+        <v>129.7</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>134.5</v>
+        <v>140.8</v>
       </c>
       <c r="G20" s="29" t="n">
         <v>122.7</v>
@@ -10124,22 +10124,22 @@
         <v>122.7</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>-1.5</v>
+        <v>-11.1</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>11.7</v>
+        <v>18</v>
       </c>
       <c r="K20" s="29" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="29" t="n">
-        <v>10.2</v>
+        <v>7</v>
       </c>
       <c r="M20" s="29" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="N20" s="29" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="O20" s="29" t="n">
         <v>6.4</v>
@@ -10167,10 +10167,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>172.1</v>
+        <v>163.2</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>168.3</v>
+        <v>180.4</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>159.1</v>
@@ -10179,22 +10179,22 @@
         <v>159.1</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>3.7</v>
+        <v>-17.2</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>9.199999999999999</v>
+        <v>21.2</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>12.9</v>
+        <v>4.1</v>
       </c>
       <c r="M21" s="18" t="n">
-        <v>29.5</v>
+        <v>25.8</v>
       </c>
       <c r="N21" s="18" t="n">
-        <v>25.2</v>
+        <v>28.1</v>
       </c>
       <c r="O21" s="18" t="n">
         <v>29.7</v>
@@ -10222,10 +10222,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>148.4</v>
+        <v>151.3</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>143.3</v>
+        <v>153.5</v>
       </c>
       <c r="G22" s="29" t="n">
         <v>144.5</v>
@@ -10234,19 +10234,19 @@
         <v>144.5</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>5.1</v>
+        <v>-2.2</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>-1.2</v>
+        <v>9</v>
       </c>
       <c r="K22" s="29" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="29" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="M22" s="29" t="n">
-        <v>-13.8</v>
+        <v>-7.3</v>
       </c>
       <c r="N22" s="29" t="n">
         <v>-14.9</v>
@@ -10277,10 +10277,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>151</v>
+        <v>148.5</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>143.7</v>
+        <v>155.2</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>147.9</v>
@@ -10289,22 +10289,22 @@
         <v>147.9</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>7.2</v>
+        <v>-6.7</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>-4.2</v>
+        <v>7.3</v>
       </c>
       <c r="K23" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="M23" s="18" t="n">
-        <v>1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="N23" s="18" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="O23" s="18" t="n">
         <v>2.3</v>
@@ -10332,10 +10332,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>172.9</v>
+        <v>173.6</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>162.9</v>
+        <v>177.7</v>
       </c>
       <c r="G24" s="29" t="n">
         <v>170.9</v>
@@ -10344,22 +10344,22 @@
         <v>170.9</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="J24" s="29" t="n">
-        <v>-8</v>
+        <v>6.7</v>
       </c>
       <c r="K24" s="29" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="29" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="M24" s="29" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N24" s="29" t="n">
         <v>14.5</v>
-      </c>
-      <c r="N24" s="29" t="n">
-        <v>13.4</v>
       </c>
       <c r="O24" s="29" t="n">
         <v>15.6</v>
@@ -10387,10 +10387,10 @@
         <v>0</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>196.6</v>
+        <v>199.6</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>192.9</v>
@@ -10399,22 +10399,22 @@
         <v>192.9</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>11.6</v>
+        <v>-7.3</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>-7.9</v>
+        <v>14.1</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>13.6</v>
+        <v>16.5</v>
       </c>
       <c r="O25" s="18" t="n">
         <v>12.8</v>
@@ -10442,10 +10442,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="29" t="n">
-        <v>176.6</v>
+        <v>187.6</v>
       </c>
       <c r="F26" s="29" t="n">
-        <v>173.6</v>
+        <v>195.1</v>
       </c>
       <c r="G26" s="29" t="n">
         <v>178.8</v>
@@ -10454,22 +10454,22 @@
         <v>178.8</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>3</v>
+        <v>-7.5</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>-5.3</v>
+        <v>16.2</v>
       </c>
       <c r="K26" s="29" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="29" t="n">
-        <v>-2.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M26" s="29" t="n">
-        <v>-10.2</v>
+        <v>-6.1</v>
       </c>
       <c r="N26" s="29" t="n">
-        <v>-6.2</v>
+        <v>-5.7</v>
       </c>
       <c r="O26" s="29" t="n">
         <v>-7.3</v>
@@ -12174,22 +12174,22 @@
         <v>0</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>178.8</v>
+        <v>207.4</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>458.1</v>
+        <v>434.2</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>54.8</v>
+        <v>51.9</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>27.7</v>
+        <v>32.1</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>26.9</v>
+        <v>31.4</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>84.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="K8" s="30">
         <f>E8+F8+G8-H8</f>
@@ -12212,22 +12212,22 @@
         <v>0</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>161.9</v>
+        <v>195.5</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>306.8</v>
+        <v>285.1</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>81.5</v>
+        <v>75.2</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>11.6</v>
+        <v>13.8</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>30.1</v>
+        <v>36.1</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>76.5</v>
+        <v>71</v>
       </c>
       <c r="K9" s="30">
         <f>E9+F9+G9-H9</f>
@@ -12250,22 +12250,22 @@
         <v>0</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>178.6</v>
+        <v>225.4</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>263.7</v>
+        <v>238.9</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>128</v>
+        <v>115.9</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>31.6</v>
+        <v>39.2</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>70</v>
+        <v>63.4</v>
       </c>
       <c r="K10" s="30">
         <f>E10+F10+G10-H10</f>
@@ -12288,22 +12288,22 @@
         <v>0</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>235.2</v>
+        <v>277.5</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>344.5</v>
+        <v>310.8</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>102.1</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>34.8</v>
+        <v>41.3</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>69.59999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="K11" s="30">
         <f>E11+F11+G11-H11</f>
@@ -12326,22 +12326,22 @@
         <v>0</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>245</v>
+        <v>292.6</v>
       </c>
       <c r="F12" s="29" t="n">
-        <v>315.8</v>
+        <v>283</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>110</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H12" s="29" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>36.8</v>
+        <v>43.8</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>64</v>
+        <v>57.3</v>
       </c>
       <c r="K12" s="30">
         <f>E12+F12+G12-H12</f>
@@ -12364,22 +12364,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>261.9</v>
+        <v>322.1</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>308.6</v>
+        <v>262.9</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>99.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>39.2</v>
+        <v>48.3</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>62.1</v>
+        <v>52.9</v>
       </c>
       <c r="K13" s="30">
         <f>E13+F13+G13-H13</f>
@@ -12402,22 +12402,22 @@
         <v>0</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>283.2</v>
+        <v>357</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>259.8</v>
+        <v>204.9</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>102.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H14" s="29" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>43.8</v>
+        <v>55.5</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>58.4</v>
+        <v>46</v>
       </c>
       <c r="K14" s="30">
         <f>E14+F14+G14-H14</f>
@@ -12440,22 +12440,22 @@
         <v>2</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>333.9</v>
+        <v>397.9</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>257</v>
+        <v>203.7</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>101.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>48.3</v>
+        <v>58.5</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>55</v>
+        <v>43.5</v>
       </c>
       <c r="K15" s="30">
         <f>E15+F15+G15-H15</f>
@@ -12542,22 +12542,22 @@
         <v>0</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>33.2</v>
+        <v>4.6</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>84.8</v>
+        <v>108.7</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>10.2</v>
+        <v>13.1</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>27</v>
+        <v>3.6</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>82.3</v>
+        <v>105.6</v>
       </c>
       <c r="K19" s="30">
         <f>E19+F19+G19-H19</f>
@@ -12580,22 +12580,22 @@
         <v>0</v>
       </c>
       <c r="E20" s="29" t="n">
-        <v>39.8</v>
+        <v>6.3</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>75.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G20" s="29" t="n">
-        <v>20.7</v>
+        <v>27</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>30</v>
+        <v>4.9</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>78.09999999999999</v>
+        <v>101</v>
       </c>
       <c r="K20" s="30">
         <f>E20+F20+G20-H20</f>
@@ -12618,22 +12618,22 @@
         <v>0</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>55.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>79.59999999999999</v>
+        <v>104.5</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>38.1</v>
+        <v>50.1</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>32.3</v>
+        <v>5.4</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>74</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K21" s="30">
         <f>E21+F21+G21-H21</f>
@@ -12656,22 +12656,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>51.7</v>
+        <v>9.5</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>75.7</v>
+        <v>109.4</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>22.5</v>
+        <v>32.7</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>34.9</v>
+        <v>6.2</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>67.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="K22" s="30">
         <f>E22+F22+G22-H22</f>
@@ -12694,22 +12694,22 @@
         <v>0</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>55.5</v>
+        <v>8</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>71.59999999999999</v>
+        <v>104.3</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>24.9</v>
+        <v>36.4</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>36.8</v>
+        <v>5.4</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>65.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="K23" s="30">
         <f>E23+F23+G23-H23</f>
@@ -12732,22 +12732,22 @@
         <v>0</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>67.7</v>
+        <v>7.6</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>80</v>
+        <v>125.7</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>25.7</v>
+        <v>40.4</v>
       </c>
       <c r="H24" s="29" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>39.2</v>
+        <v>4.4</v>
       </c>
       <c r="J24" s="29" t="n">
-        <v>61.8</v>
+        <v>97.2</v>
       </c>
       <c r="K24" s="30">
         <f>E24+F24+G24-H24</f>
@@ -12770,22 +12770,22 @@
         <v>0</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>86.2</v>
+        <v>12.4</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>79.09999999999999</v>
+        <v>134</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>31.3</v>
+        <v>53.2</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>43.8</v>
+        <v>6.2</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>57.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K25" s="30">
         <f>E25+F25+G25-H25</f>
@@ -12808,22 +12808,22 @@
         <v>2</v>
       </c>
       <c r="E26" s="29" t="n">
-        <v>85.59999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="F26" s="29" t="n">
-        <v>63.7</v>
+        <v>117</v>
       </c>
       <c r="G26" s="29" t="n">
-        <v>27.4</v>
+        <v>49</v>
       </c>
       <c r="H26" s="29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>48.5</v>
+        <v>11.5</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>51</v>
+        <v>92.8</v>
       </c>
       <c r="K26" s="30">
         <f>E26+F26+G26-H26</f>
@@ -14008,7 +14008,7 @@
         <v>2019</v>
       </c>
       <c r="B8" s="29" t="n">
-        <v>-6.2</v>
+        <v>-5.9</v>
       </c>
       <c r="C8" s="29" t="n">
         <v>7</v>
@@ -14027,7 +14027,7 @@
         <v>2020</v>
       </c>
       <c r="B9" s="18" t="n">
-        <v>-0.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>7</v>
@@ -14046,7 +14046,7 @@
         <v>2021</v>
       </c>
       <c r="B10" s="29" t="n">
-        <v>10.6</v>
+        <v>31.5</v>
       </c>
       <c r="C10" s="29" t="n">
         <v>7</v>
@@ -14065,7 +14065,7 @@
         <v>2022</v>
       </c>
       <c r="B11" s="18" t="n">
-        <v>23.1</v>
+        <v>30.4</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>7</v>
@@ -14084,7 +14084,7 @@
         <v>2023</v>
       </c>
       <c r="B12" s="29" t="n">
-        <v>31.8</v>
+        <v>45.7</v>
       </c>
       <c r="C12" s="29" t="n">
         <v>7</v>
@@ -14103,7 +14103,7 @@
         <v>2024</v>
       </c>
       <c r="B13" s="18" t="n">
-        <v>38.5</v>
+        <v>52.5</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>7</v>
@@ -14122,7 +14122,7 @@
         <v>2025</v>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.8</v>
+        <v>56.7</v>
       </c>
       <c r="C14" s="29" t="n">
         <v>7</v>
@@ -14141,7 +14141,7 @@
         <v>2026</v>
       </c>
       <c r="B15" s="18" t="n">
-        <v>9.9</v>
+        <v>20.5</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>7</v>
@@ -14194,7 +14194,7 @@
         <v>2019</v>
       </c>
       <c r="B19" s="18" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="C19" s="18" t="n">
         <v>7</v>
@@ -14213,7 +14213,7 @@
         <v>2020</v>
       </c>
       <c r="B20" s="29" t="n">
-        <v>-1.5</v>
+        <v>-11.1</v>
       </c>
       <c r="C20" s="29" t="n">
         <v>7</v>
@@ -14232,7 +14232,7 @@
         <v>2021</v>
       </c>
       <c r="B21" s="18" t="n">
-        <v>3.7</v>
+        <v>-17.2</v>
       </c>
       <c r="C21" s="18" t="n">
         <v>7</v>
@@ -14251,7 +14251,7 @@
         <v>2022</v>
       </c>
       <c r="B22" s="29" t="n">
-        <v>5.1</v>
+        <v>-2.2</v>
       </c>
       <c r="C22" s="29" t="n">
         <v>7</v>
@@ -14270,7 +14270,7 @@
         <v>2023</v>
       </c>
       <c r="B23" s="18" t="n">
-        <v>7.2</v>
+        <v>-6.7</v>
       </c>
       <c r="C23" s="18" t="n">
         <v>7</v>
@@ -14289,7 +14289,7 @@
         <v>2024</v>
       </c>
       <c r="B24" s="29" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="C24" s="29" t="n">
         <v>7</v>
@@ -14308,7 +14308,7 @@
         <v>2025</v>
       </c>
       <c r="B25" s="18" t="n">
-        <v>11.6</v>
+        <v>-7.3</v>
       </c>
       <c r="C25" s="18" t="n">
         <v>7</v>
@@ -14327,7 +14327,7 @@
         <v>2026</v>
       </c>
       <c r="B26" s="29" t="n">
-        <v>3</v>
+        <v>-7.5</v>
       </c>
       <c r="C26" s="29" t="n">
         <v>7</v>
@@ -15006,16 +15006,16 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>36.82</v>
+        <v>40.47</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>27.74</v>
+        <v>33.39</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>-9.08</v>
+        <v>-7.08</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-24.7</v>
+        <v>-17.5</v>
       </c>
     </row>
     <row r="9">
@@ -15025,13 +15025,13 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>1.0137</v>
+        <v>0.9222</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1.2269</v>
+        <v>1.0192</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.2132</v>
+        <v>0.097</v>
       </c>
       <c r="E9" s="11" t="n"/>
     </row>
@@ -15066,7 +15066,7 @@
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="14">
@@ -15076,7 +15076,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>-11.15</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="15">
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>-1.21</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="16">
@@ -15096,7 +15096,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5.92</v>
+        <v>3.24</v>
       </c>
       <c r="D16" s="31">
         <f>SUM(B13:B16)</f>
@@ -15183,19 +15183,19 @@
         <v>10.7</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>6.321</v>
+        <v>6.927</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>4.881</v>
+        <v>5.789</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>-22.8</v>
+        <v>-16.4</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>19.3</v>
+        <v>21.16</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>16.5</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="22">
@@ -15214,19 +15214,19 @@
         <v>-12.3</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>5.482</v>
+        <v>6.18</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>4.803</v>
+        <v>5.731</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>-12.4</v>
+        <v>-7.3</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>5.08</v>
+        <v>5.73</v>
       </c>
       <c r="I22" s="32" t="n">
-        <v>3.9</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="23">
@@ -15245,19 +15245,19 @@
         <v>13.5</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>6.832</v>
+        <v>7.466</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>3.552</v>
+        <v>4.437</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>-48</v>
+        <v>-40.6</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>12.43</v>
+        <v>13.58</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>7.34</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="26">
@@ -15299,16 +15299,16 @@
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>-4.4</v>
+        <v>-3.47</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>-0.47</v>
+        <v>-0.38</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>-2.81</v>
+        <v>-1.59</v>
       </c>
       <c r="F27" s="31">
         <f>B27+C27+D27</f>
@@ -15322,16 +15322,16 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>-0.63</v>
+        <v>-0.71</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>-0.63</v>
+        <v>-0.42</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>-1.18</v>
+        <v>-1.07</v>
       </c>
       <c r="F28" s="31">
         <f>B28+C28+D28</f>
@@ -15345,16 +15345,16 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>-5.97</v>
+        <v>-5.51</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>-5.09</v>
+        <v>-4.42</v>
       </c>
       <c r="F29" s="31">
         <f>B29+C29+D29</f>
@@ -15368,16 +15368,16 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>3.11</v>
+        <v>3.39</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>-11</v>
+        <v>-9.4</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>-1.19</v>
+        <v>-1.07</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>-9.08</v>
+        <v>-7.08</v>
       </c>
       <c r="F30" s="31">
         <f>B30+C30+D30</f>
@@ -15506,7 +15506,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Cuotas del periodo reciente aplicadas a los litros del periodo previo, con las cinco bases de volumen y los dos periodos previos. IEPS observado del periodo reciente: 34.03. Rango de la aportación del volumen: -0.01 a +2.35 contra ene-2025 a mar-2026 y -1.82 a +2.59 contra ene a mar de 2026.</t>
+          <t>Cuotas del periodo reciente aplicadas a los litros del periodo previo, con las cinco bases de volumen y los dos periodos previos. IEPS observado del periodo reciente: 34.03. Rango de la aportación del volumen: +0.01 a +2.37 contra ene-2025 a mar-2026 y -1.83 a +2.60 contra ene a mar de 2026.</t>
         </is>
       </c>
     </row>
@@ -15581,19 +15581,19 @@
         <v>7.9</v>
       </c>
       <c r="F40" s="32" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="G40" s="32" t="n">
-        <v>31.68</v>
+        <v>31.67</v>
       </c>
       <c r="H40" s="32" t="n">
         <v>4.7</v>
       </c>
       <c r="I40" s="32" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="J40" s="32" t="n">
-        <v>32.69</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="41">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="B41" s="22" t="n">
-        <v>6.183</v>
+        <v>6.184</v>
       </c>
       <c r="C41" s="22" t="n">
         <v>6.55</v>
@@ -15615,19 +15615,19 @@
         <v>0.4</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="G41" s="22" t="n">
-        <v>34.04</v>
+        <v>34.02</v>
       </c>
       <c r="H41" s="22" t="n">
         <v>-5.2</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>-1.82</v>
+        <v>-1.83</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>35.85</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="42">
@@ -15640,7 +15640,7 @@
         <v>5.779</v>
       </c>
       <c r="C42" s="32" t="n">
-        <v>5.975</v>
+        <v>5.974</v>
       </c>
       <c r="D42" s="32" t="n">
         <v>6.218</v>
@@ -15649,19 +15649,19 @@
         <v>7.6</v>
       </c>
       <c r="F42" s="32" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="G42" s="32" t="n">
-        <v>31.77</v>
+        <v>31.75</v>
       </c>
       <c r="H42" s="32" t="n">
         <v>4.1</v>
       </c>
       <c r="I42" s="32" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="J42" s="32" t="n">
-        <v>32.87</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="43">
@@ -15683,19 +15683,19 @@
         <v>6.4</v>
       </c>
       <c r="F43" s="22" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G43" s="22" t="n">
-        <v>32.08</v>
+        <v>32.06</v>
       </c>
       <c r="H43" s="22" t="n">
         <v>8.5</v>
       </c>
       <c r="I43" s="22" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>31.44</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="44">
@@ -15717,19 +15717,19 @@
         <v>6.1</v>
       </c>
       <c r="F44" s="32" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G44" s="32" t="n">
-        <v>32.16</v>
+        <v>32.14</v>
       </c>
       <c r="H44" s="32" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="I44" s="32" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="J44" s="32" t="n">
-        <v>31.52</v>
+        <v>31.51</v>
       </c>
     </row>
   </sheetData>
@@ -31748,7 +31748,7 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Jan-2017</t>
+          <t>Jan-2019</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -31757,7 +31757,7 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -31773,7 +31773,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Jan-2017</t>
+          <t>Jan-2019</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -31782,7 +31782,7 @@
         </is>
       </c>
       <c r="E9" s="13" t="n">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -31923,7 +31923,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Jan-2017</t>
+          <t>Jan-2019</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
@@ -31932,7 +31932,7 @@
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -31948,7 +31948,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Jan-2017</t>
+          <t>Jan-2019</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -31957,7 +31957,7 @@
         </is>
       </c>
       <c r="E16" s="16" t="n">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
